--- a/consolidacion/data/pruebas/viviendas_gestion_riesgo_20260814_0800.xlsx
+++ b/consolidacion/data/pruebas/viviendas_gestion_riesgo_20260814_0800.xlsx
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Secretar&lt;c3&gt;&lt;ad&gt;a de Gesti&lt;c3&gt;&lt;b3&gt;n del Riesgo</t>
+          <t>Secretaría de Gestión del Riesgo</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>S&lt;c3&gt;&lt;ad&gt;</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
